--- a/reporte_Clasico.xlsx
+++ b/reporte_Clasico.xlsx
@@ -751,7 +751,7 @@
         <is>
           <t>Empresa: BBVA
 Usuario: Uriel Meneses
-Fecha de descarga: 11-03-2026
+Fecha de descarga: 12-03-2026
 Descarga por Fecha de publicación del 2026-01-01 al 2026-01-31</t>
         </is>
       </c>
